--- a/construction_template/data/templates_blank/daily_log_c1.xlsx
+++ b/construction_template/data/templates_blank/daily_log_c1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.168\web\files\任泰-施工管理系統\demo\template_dailyRecord\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.168\03.開發\100.外部\任泰-施工管理系統\12.Backend\alpha\public\template_dailyRecord\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E393A56B-85DC-4A84-93B9-AC22A0CB7748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE63C649-6869-4A3D-A2A9-CAEE1AD58192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12570" yWindow="1635" windowWidth="22260" windowHeight="12240" xr2:uid="{E59D0174-199A-4893-98FA-751BCFAADE09}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E59D0174-199A-4893-98FA-751BCFAADE09}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -231,12 +231,48 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>${table:materialItems.quantity}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>${table:materialItems.doneQ</t>
+    <r>
+      <t>${table:constructionItems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>.unit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>${table:constructionItems.quantity}</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>${table:constructionItems.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>doneQ</t>
     </r>
     <r>
       <rPr>
@@ -252,7 +288,17 @@
   </si>
   <si>
     <r>
-      <t>${table:materialItems.totalQ</t>
+      <t>${table:constructionItems.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>totalQ</t>
     </r>
     <r>
       <rPr>
@@ -267,6 +313,42 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
+    <t>${table:materialItems.quantity}</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>${table:materialItems.doneQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>uantity}</t>
+    </r>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>${table:materialItems.totalQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="標楷體"/>
+        <family val="4"/>
+        <charset val="136"/>
+      </rPr>
+      <t>uantity}</t>
+    </r>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>${table:manUsage.</t>
     </r>
@@ -427,6 +509,10 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
+    <t>${table:constructionItems.description}</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
     <t>${table:materialItems.description}</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
@@ -505,6 +591,10 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
+    <t>${table:constructionItems.note}</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
     <t>${table:materialItems.note}</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
@@ -630,30 +720,6 @@
       </rPr>
       <t>（此項如勾選“有”，則應填寫後附「公共工程施工日誌 之技術士簽章表」）</t>
     </r>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.description}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.unit}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.quantity}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.doneQuantity}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.totalQuantity}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>${table:projectSheets.note}</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
@@ -1354,7 +1420,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1415,12 +1481,276 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="23" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1428,9 +1758,99 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="32" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="34" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1458,236 +1878,14 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="32" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1695,155 +1893,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2192,335 +2261,335 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="25.5">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
     </row>
     <row r="2" spans="1:22" ht="25.5">
-      <c r="A2" s="129" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="125" t="s">
-        <v>61</v>
-      </c>
-      <c r="T2" s="125"/>
-      <c r="U2" s="125"/>
-      <c r="V2" s="125"/>
+      <c r="A2" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="51" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="52" t="s">
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="52"/>
-      <c r="P3" s="126" t="s">
+      <c r="O3" s="94"/>
+      <c r="P3" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="127" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="128"/>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
     </row>
     <row r="4" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="121" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="91" t="s">
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="92"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="115" t="s">
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116"/>
-      <c r="V4" s="117"/>
+      <c r="Q4" s="104"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="104"/>
+      <c r="T4" s="104"/>
+      <c r="U4" s="104"/>
+      <c r="V4" s="105"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="135" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="75" t="s">
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="136" t="s">
+      <c r="H5" s="33"/>
+      <c r="I5" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="118" t="s">
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="120"/>
-      <c r="N5" s="136" t="s">
+      <c r="M5" s="47"/>
+      <c r="N5" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="137"/>
-      <c r="P5" s="118" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="75" t="s">
-        <v>65</v>
-      </c>
-      <c r="T5" s="75"/>
-      <c r="U5" s="75"/>
-      <c r="V5" s="75"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="154" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="155"/>
-      <c r="I6" s="155"/>
-      <c r="J6" s="155"/>
-      <c r="K6" s="156"/>
-      <c r="L6" s="91" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="157" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="155"/>
-      <c r="R6" s="155"/>
-      <c r="S6" s="155"/>
-      <c r="T6" s="155"/>
-      <c r="U6" s="155"/>
-      <c r="V6" s="156"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="24"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="158" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="159"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="159"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="92" t="s">
+      <c r="L7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="160" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q7" s="161"/>
-      <c r="R7" s="161"/>
-      <c r="S7" s="161"/>
-      <c r="T7" s="161"/>
-      <c r="U7" s="162" t="s">
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="V7" s="163"/>
+      <c r="V7" s="71"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="148" t="s">
+      <c r="A8" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="149"/>
-      <c r="C8" s="149"/>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="149"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="149"/>
-      <c r="M8" s="149"/>
-      <c r="N8" s="149"/>
-      <c r="O8" s="149"/>
-      <c r="P8" s="149"/>
-      <c r="Q8" s="149"/>
-      <c r="R8" s="149"/>
-      <c r="S8" s="149"/>
-      <c r="T8" s="149"/>
-      <c r="U8" s="149"/>
-      <c r="V8" s="150"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
+      <c r="V8" s="108"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="83" t="s">
+      <c r="I9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83" t="s">
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="87" t="s">
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="88"/>
-      <c r="Q9" s="89"/>
-      <c r="R9" s="151" t="s">
+      <c r="P9" s="56"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="152"/>
-      <c r="T9" s="152"/>
-      <c r="U9" s="152"/>
-      <c r="V9" s="153"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="109"/>
     </row>
     <row r="10" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A10" s="143" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="144"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="144"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
+      <c r="A10" s="110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
       <c r="H10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="142" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10" s="142"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" s="77"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="84" t="s">
-        <v>87</v>
-      </c>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
-      <c r="V10" s="78"/>
+        <v>46</v>
+      </c>
+      <c r="I10" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="68"/>
     </row>
     <row r="11" spans="1:22" ht="17.25" hidden="1" thickBot="1">
-      <c r="A11" s="23"/>
+      <c r="A11" s="111"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2544,92 +2613,92 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="17.25" thickTop="1">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="139"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="139"/>
-      <c r="G12" s="140"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="141"/>
-      <c r="O12" s="100"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="101"/>
-      <c r="U12" s="101"/>
-      <c r="V12" s="105"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="154"/>
     </row>
     <row r="13" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="155" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="156" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="157"/>
+      <c r="H13" s="158" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="112" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="114" t="s">
-        <v>70</v>
-      </c>
-      <c r="J13" s="114"/>
-      <c r="K13" s="114"/>
-      <c r="L13" s="114" t="s">
-        <v>71</v>
-      </c>
-      <c r="M13" s="114"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="102" t="s">
-        <v>72</v>
-      </c>
-      <c r="P13" s="103"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="102" t="s">
-        <v>73</v>
-      </c>
-      <c r="S13" s="103"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="103"/>
-      <c r="V13" s="106"/>
+      <c r="I13" s="159" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="159" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="159"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="160" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" s="161"/>
+      <c r="Q13" s="162"/>
+      <c r="R13" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="S13" s="161"/>
+      <c r="T13" s="161"/>
+      <c r="U13" s="161"/>
+      <c r="V13" s="163"/>
     </row>
     <row r="14" spans="1:22" ht="17.25" hidden="1" thickBot="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="34"/>
+      <c r="A14" s="144"/>
+      <c r="B14" s="145"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="148"/>
+      <c r="M14" s="149"/>
+      <c r="N14" s="150"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="151"/>
+      <c r="Q14" s="151"/>
+      <c r="R14" s="148"/>
+      <c r="S14" s="151"/>
+      <c r="T14" s="151"/>
+      <c r="U14" s="151"/>
+      <c r="V14" s="152"/>
     </row>
     <row r="15" spans="1:22" ht="17.25" hidden="1" thickBot="1">
       <c r="A15" s="14"/>
@@ -2653,490 +2722,490 @@
       <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="18"/>
-      <c r="V15" s="24"/>
+      <c r="V15" s="112"/>
     </row>
     <row r="16" spans="1:22" ht="17.25" thickTop="1">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="146"/>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="146"/>
-      <c r="R16" s="146"/>
-      <c r="S16" s="146"/>
-      <c r="T16" s="146"/>
-      <c r="U16" s="146"/>
-      <c r="V16" s="147"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="114"/>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="132"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="107" t="s">
+      <c r="I17" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="108"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="134" t="s">
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="134"/>
-      <c r="N17" s="134"/>
-      <c r="O17" s="107" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="108"/>
-      <c r="Q17" s="108"/>
-      <c r="R17" s="109" t="s">
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="S17" s="110"/>
-      <c r="T17" s="110"/>
-      <c r="U17" s="110"/>
-      <c r="V17" s="111"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="116"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="81"/>
+      <c r="A18" s="117" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="80"/>
       <c r="H18" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I18" s="76" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J18" s="77"/>
       <c r="K18" s="78"/>
       <c r="L18" s="76" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M18" s="77"/>
       <c r="N18" s="78"/>
-      <c r="O18" s="84" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="S18" s="85"/>
-      <c r="T18" s="85"/>
-      <c r="U18" s="85"/>
-      <c r="V18" s="86"/>
+      <c r="O18" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="68"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="82"/>
-      <c r="T19" s="82"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="82"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75" t="s">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75" t="s">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="75"/>
-      <c r="J20" s="75"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="83" t="s">
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="83"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="87" t="s">
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="P20" s="88"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="91" t="s">
+      <c r="P20" s="56"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="S20" s="92"/>
-      <c r="T20" s="92"/>
-      <c r="U20" s="92"/>
-      <c r="V20" s="93"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="21"/>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="74" t="s">
+        <v>56</v>
+      </c>
+      <c r="S21" s="73"/>
+      <c r="T21" s="73"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="73"/>
+    </row>
+    <row r="22" spans="1:22" ht="16.5" hidden="1" customHeight="1">
+      <c r="A22" s="118"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="82"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="119"/>
+    </row>
+    <row r="23" spans="1:22" ht="23.25" customHeight="1">
+      <c r="A23" s="120" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="121"/>
+    </row>
+    <row r="24" spans="1:22" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A24" s="122"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="84"/>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="84"/>
+      <c r="T24" s="84"/>
+      <c r="U24" s="84"/>
+      <c r="V24" s="123"/>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="124" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="125"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="125"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="125"/>
+      <c r="O25" s="125"/>
+      <c r="P25" s="125"/>
+      <c r="Q25" s="125"/>
+      <c r="R25" s="125"/>
+      <c r="S25" s="125"/>
+      <c r="T25" s="125"/>
+      <c r="U25" s="125"/>
+      <c r="V25" s="126"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="127" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="128"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="128"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="128"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128"/>
+      <c r="Q26" s="128"/>
+      <c r="R26" s="128"/>
+      <c r="S26" s="128"/>
+      <c r="T26" s="128"/>
+      <c r="U26" s="128"/>
+      <c r="V26" s="129"/>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="128"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="128"/>
+      <c r="P27" s="128"/>
+      <c r="Q27" s="128"/>
+      <c r="R27" s="128"/>
+      <c r="S27" s="128"/>
+      <c r="T27" s="128"/>
+      <c r="U27" s="128"/>
+      <c r="V27" s="129"/>
+    </row>
+    <row r="28" spans="1:22" ht="31.5" customHeight="1">
+      <c r="A28" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="128"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="128"/>
+      <c r="Q28" s="128"/>
+      <c r="R28" s="128"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="128"/>
+      <c r="U28" s="128"/>
+      <c r="V28" s="129"/>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" s="127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="128"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="128"/>
+      <c r="K29" s="128"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="128"/>
+      <c r="P29" s="128"/>
+      <c r="Q29" s="128"/>
+      <c r="R29" s="128"/>
+      <c r="S29" s="128"/>
+      <c r="T29" s="128"/>
+      <c r="U29" s="128"/>
+      <c r="V29" s="129"/>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" s="127" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="128"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="128"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="128"/>
+      <c r="N30" s="128"/>
+      <c r="O30" s="128"/>
+      <c r="P30" s="128"/>
+      <c r="Q30" s="128"/>
+      <c r="R30" s="128"/>
+      <c r="S30" s="128"/>
+      <c r="T30" s="128"/>
+      <c r="U30" s="128"/>
+      <c r="V30" s="129"/>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="A31" s="131" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="85"/>
+      <c r="T31" s="85"/>
+      <c r="U31" s="85"/>
+      <c r="V31" s="132"/>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" s="133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="75"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="95" t="s">
-        <v>50</v>
-      </c>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="M21" s="75"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="90" t="s">
-        <v>51</v>
-      </c>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="90"/>
-      <c r="R21" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95"/>
-      <c r="U21" s="95"/>
-      <c r="V21" s="95"/>
-    </row>
-    <row r="22" spans="1:22" ht="16.5" hidden="1" customHeight="1">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="38"/>
-      <c r="U22" s="38"/>
-      <c r="V22" s="39"/>
-    </row>
-    <row r="23" spans="1:22" ht="23.25" customHeight="1">
-      <c r="A23" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="46"/>
-      <c r="P23" s="46"/>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="46"/>
-      <c r="V23" s="47"/>
-    </row>
-    <row r="24" spans="1:22" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A24" s="48"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="49"/>
-      <c r="S24" s="49"/>
-      <c r="T24" s="49"/>
-      <c r="U24" s="49"/>
-      <c r="V24" s="50"/>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="58"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="60"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="61"/>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="61"/>
-    </row>
-    <row r="28" spans="1:22" ht="31.5" customHeight="1">
-      <c r="A28" s="62" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="60"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="61"/>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="A29" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="60"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="60"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="61"/>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="60"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="60"/>
-      <c r="O30" s="60"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="61"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="64"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
-      <c r="R31" s="64"/>
-      <c r="S31" s="64"/>
-      <c r="T31" s="64"/>
-      <c r="U31" s="64"/>
-      <c r="V31" s="65"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="67"/>
-      <c r="C32" s="67"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="69"/>
-      <c r="P32" s="69"/>
-      <c r="Q32" s="69"/>
-      <c r="R32" s="69"/>
-      <c r="S32" s="69"/>
-      <c r="T32" s="69"/>
-      <c r="U32" s="69"/>
-      <c r="V32" s="70"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="91"/>
+      <c r="R32" s="91"/>
+      <c r="S32" s="91"/>
+      <c r="T32" s="91"/>
+      <c r="U32" s="91"/>
+      <c r="V32" s="134"/>
     </row>
     <row r="33" spans="1:22">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="135" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="2"/>
@@ -3145,205 +3214,130 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="54"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="55"/>
+      <c r="H33" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="89"/>
+      <c r="O33" s="89"/>
+      <c r="P33" s="89"/>
+      <c r="Q33" s="89"/>
+      <c r="R33" s="89"/>
+      <c r="S33" s="89"/>
+      <c r="T33" s="89"/>
+      <c r="U33" s="89"/>
+      <c r="V33" s="136"/>
     </row>
     <row r="34" spans="1:22">
-      <c r="A34" s="96" t="s">
+      <c r="A34" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="97"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="98"/>
-      <c r="O34" s="98"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="98"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="98"/>
-      <c r="T34" s="98"/>
-      <c r="U34" s="98"/>
-      <c r="V34" s="99"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="65"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="65"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="138"/>
     </row>
     <row r="35" spans="1:22" ht="17.25" thickBot="1">
-      <c r="A35" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="72"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="72"/>
-      <c r="O35" s="72"/>
-      <c r="P35" s="72"/>
-      <c r="Q35" s="72"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
-      <c r="T35" s="72"/>
-      <c r="U35" s="72"/>
-      <c r="V35" s="73"/>
+      <c r="A35" s="139" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="87"/>
+      <c r="N35" s="87"/>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="87"/>
+      <c r="S35" s="87"/>
+      <c r="T35" s="87"/>
+      <c r="U35" s="87"/>
+      <c r="V35" s="140"/>
     </row>
     <row r="36" spans="1:22" ht="17.25" thickTop="1">
-      <c r="A36" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="42"/>
+      <c r="A36" s="141" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="142"/>
+      <c r="C36" s="142"/>
+      <c r="D36" s="142"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
+      <c r="M36" s="142"/>
+      <c r="N36" s="142"/>
+      <c r="O36" s="142"/>
+      <c r="P36" s="142"/>
+      <c r="Q36" s="142"/>
+      <c r="R36" s="142"/>
+      <c r="S36" s="142"/>
+      <c r="T36" s="142"/>
+      <c r="U36" s="142"/>
+      <c r="V36" s="143"/>
     </row>
     <row r="37" spans="1:22" ht="171" customHeight="1">
-      <c r="A37" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="44"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="44"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
-      <c r="R37" s="44"/>
-      <c r="S37" s="44"/>
-      <c r="T37" s="44"/>
-      <c r="U37" s="44"/>
-      <c r="V37" s="44"/>
+      <c r="A37" s="164" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="100"/>
+      <c r="J37" s="100"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="100"/>
+      <c r="M37" s="100"/>
+      <c r="N37" s="100"/>
+      <c r="O37" s="100"/>
+      <c r="P37" s="100"/>
+      <c r="Q37" s="100"/>
+      <c r="R37" s="100"/>
+      <c r="S37" s="100"/>
+      <c r="T37" s="100"/>
+      <c r="U37" s="100"/>
+      <c r="V37" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="P6:V6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="A16:V16"/>
-    <mergeCell ref="A8:V8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="R9:V9"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:V10"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="D2:R2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="P4:V4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="D4:K4"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="H34:V34"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="R12:V12"/>
-    <mergeCell ref="R13:V13"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="A19:V19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="R18:V18"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="R20:V20"/>
-    <mergeCell ref="R21:V21"/>
     <mergeCell ref="A22:V22"/>
     <mergeCell ref="A36:V36"/>
     <mergeCell ref="A37:V37"/>
@@ -3360,6 +3354,81 @@
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="H32:V32"/>
     <mergeCell ref="A35:V35"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="A19:V19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="R18:V18"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R20:V20"/>
+    <mergeCell ref="R21:V21"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="H34:V34"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="R10:V10"/>
+    <mergeCell ref="R12:V12"/>
+    <mergeCell ref="R13:V13"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="D4:K4"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="D2:R2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A16:V16"/>
+    <mergeCell ref="A8:V8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="R9:V9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="P6:V6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="U7:V7"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
